--- a/预测水位/OutputData/SK05(out).xlsx
+++ b/预测水位/OutputData/SK05(out).xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2161"/>
+  <dimension ref="A1:B2209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17726,6 +17726,390 @@
         <v>591.647</v>
       </c>
     </row>
+    <row r="2162">
+      <c r="A2162" s="2" t="n">
+        <v>45838</v>
+      </c>
+      <c r="B2162" t="n">
+        <v>591.657</v>
+      </c>
+    </row>
+    <row r="2163">
+      <c r="A2163" s="2" t="n">
+        <v>45838.08333333334</v>
+      </c>
+      <c r="B2163" t="n">
+        <v>591.659</v>
+      </c>
+    </row>
+    <row r="2164">
+      <c r="A2164" s="2" t="n">
+        <v>45838.16666666666</v>
+      </c>
+      <c r="B2164" t="n">
+        <v>591.6609999999999</v>
+      </c>
+    </row>
+    <row r="2165">
+      <c r="A2165" s="2" t="n">
+        <v>45838.25</v>
+      </c>
+      <c r="B2165" t="n">
+        <v>591.644</v>
+      </c>
+    </row>
+    <row r="2166">
+      <c r="A2166" s="2" t="n">
+        <v>45838.33333333334</v>
+      </c>
+      <c r="B2166" t="n">
+        <v>591.625</v>
+      </c>
+    </row>
+    <row r="2167">
+      <c r="A2167" s="2" t="n">
+        <v>45838.41666666666</v>
+      </c>
+      <c r="B2167" t="n">
+        <v>591.614</v>
+      </c>
+    </row>
+    <row r="2168">
+      <c r="A2168" s="2" t="n">
+        <v>45838.5</v>
+      </c>
+      <c r="B2168" t="n">
+        <v>591.601</v>
+      </c>
+    </row>
+    <row r="2169">
+      <c r="A2169" s="2" t="n">
+        <v>45838.58333333334</v>
+      </c>
+      <c r="B2169" t="n">
+        <v>591.591</v>
+      </c>
+    </row>
+    <row r="2170">
+      <c r="A2170" s="2" t="n">
+        <v>45838.66666666666</v>
+      </c>
+      <c r="B2170" t="n">
+        <v>591.581</v>
+      </c>
+    </row>
+    <row r="2171">
+      <c r="A2171" s="2" t="n">
+        <v>45838.75</v>
+      </c>
+      <c r="B2171" t="n">
+        <v>591.579</v>
+      </c>
+    </row>
+    <row r="2172">
+      <c r="A2172" s="2" t="n">
+        <v>45838.83333333334</v>
+      </c>
+      <c r="B2172" t="n">
+        <v>591.583</v>
+      </c>
+    </row>
+    <row r="2173">
+      <c r="A2173" s="2" t="n">
+        <v>45838.91666666666</v>
+      </c>
+      <c r="B2173" t="n">
+        <v>591.5839999999999</v>
+      </c>
+    </row>
+    <row r="2174">
+      <c r="A2174" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B2174" t="n">
+        <v>591.5890000000001</v>
+      </c>
+    </row>
+    <row r="2175">
+      <c r="A2175" s="2" t="n">
+        <v>45839.08333333334</v>
+      </c>
+      <c r="B2175" t="n">
+        <v>591.5839999999999</v>
+      </c>
+    </row>
+    <row r="2176">
+      <c r="A2176" s="2" t="n">
+        <v>45839.16666666666</v>
+      </c>
+      <c r="B2176" t="n">
+        <v>591.566</v>
+      </c>
+    </row>
+    <row r="2177">
+      <c r="A2177" s="2" t="n">
+        <v>45839.25</v>
+      </c>
+      <c r="B2177" t="n">
+        <v>591.524</v>
+      </c>
+    </row>
+    <row r="2178">
+      <c r="A2178" s="2" t="n">
+        <v>45839.33333333334</v>
+      </c>
+      <c r="B2178" t="n">
+        <v>591.519</v>
+      </c>
+    </row>
+    <row r="2179">
+      <c r="A2179" s="2" t="n">
+        <v>45839.41666666666</v>
+      </c>
+      <c r="B2179" t="n">
+        <v>591.51</v>
+      </c>
+    </row>
+    <row r="2180">
+      <c r="A2180" s="2" t="n">
+        <v>45839.5</v>
+      </c>
+      <c r="B2180" t="n">
+        <v>591.484</v>
+      </c>
+    </row>
+    <row r="2181">
+      <c r="A2181" s="2" t="n">
+        <v>45839.58333333334</v>
+      </c>
+      <c r="B2181" t="n">
+        <v>591.446</v>
+      </c>
+    </row>
+    <row r="2182">
+      <c r="A2182" s="2" t="n">
+        <v>45839.66666666666</v>
+      </c>
+      <c r="B2182" t="n">
+        <v>591.4829999999999</v>
+      </c>
+    </row>
+    <row r="2183">
+      <c r="A2183" s="2" t="n">
+        <v>45839.75</v>
+      </c>
+      <c r="B2183" t="n">
+        <v>591.486</v>
+      </c>
+    </row>
+    <row r="2184">
+      <c r="A2184" s="2" t="n">
+        <v>45839.83333333334</v>
+      </c>
+      <c r="B2184" t="n">
+        <v>591.491</v>
+      </c>
+    </row>
+    <row r="2185">
+      <c r="A2185" s="2" t="n">
+        <v>45839.91666666666</v>
+      </c>
+      <c r="B2185" t="n">
+        <v>591.497</v>
+      </c>
+    </row>
+    <row r="2186">
+      <c r="A2186" s="2" t="n">
+        <v>45840</v>
+      </c>
+      <c r="B2186" t="n">
+        <v>591.505</v>
+      </c>
+    </row>
+    <row r="2187">
+      <c r="A2187" s="2" t="n">
+        <v>45840.08333333334</v>
+      </c>
+      <c r="B2187" t="n">
+        <v>591.498</v>
+      </c>
+    </row>
+    <row r="2188">
+      <c r="A2188" s="2" t="n">
+        <v>45840.16666666666</v>
+      </c>
+      <c r="B2188" t="n">
+        <v>591.471</v>
+      </c>
+    </row>
+    <row r="2189">
+      <c r="A2189" s="2" t="n">
+        <v>45840.25</v>
+      </c>
+      <c r="B2189" t="n">
+        <v>591.456</v>
+      </c>
+    </row>
+    <row r="2190">
+      <c r="A2190" s="2" t="n">
+        <v>45840.33333333334</v>
+      </c>
+      <c r="B2190" t="n">
+        <v>591.442</v>
+      </c>
+    </row>
+    <row r="2191">
+      <c r="A2191" s="2" t="n">
+        <v>45840.41666666666</v>
+      </c>
+      <c r="B2191" t="n">
+        <v>591.439</v>
+      </c>
+    </row>
+    <row r="2192">
+      <c r="A2192" s="2" t="n">
+        <v>45840.5</v>
+      </c>
+      <c r="B2192" t="n">
+        <v>591.428</v>
+      </c>
+    </row>
+    <row r="2193">
+      <c r="A2193" s="2" t="n">
+        <v>45840.58333333334</v>
+      </c>
+      <c r="B2193" t="n">
+        <v>591.413</v>
+      </c>
+    </row>
+    <row r="2194">
+      <c r="A2194" s="2" t="n">
+        <v>45840.66666666666</v>
+      </c>
+      <c r="B2194" t="n">
+        <v>591.395</v>
+      </c>
+    </row>
+    <row r="2195">
+      <c r="A2195" s="2" t="n">
+        <v>45840.75</v>
+      </c>
+      <c r="B2195" t="n">
+        <v>591.399</v>
+      </c>
+    </row>
+    <row r="2196">
+      <c r="A2196" s="2" t="n">
+        <v>45840.83333333334</v>
+      </c>
+      <c r="B2196" t="n">
+        <v>591.4160000000001</v>
+      </c>
+    </row>
+    <row r="2197">
+      <c r="A2197" s="2" t="n">
+        <v>45840.91666666666</v>
+      </c>
+      <c r="B2197" t="n">
+        <v>591.432</v>
+      </c>
+    </row>
+    <row r="2198">
+      <c r="A2198" s="2" t="n">
+        <v>45841</v>
+      </c>
+      <c r="B2198" t="n">
+        <v>591.4400000000001</v>
+      </c>
+    </row>
+    <row r="2199">
+      <c r="A2199" s="2" t="n">
+        <v>45841.08333333334</v>
+      </c>
+      <c r="B2199" t="n">
+        <v>591.441</v>
+      </c>
+    </row>
+    <row r="2200">
+      <c r="A2200" s="2" t="n">
+        <v>45841.16666666666</v>
+      </c>
+      <c r="B2200" t="n">
+        <v>591.4160000000001</v>
+      </c>
+    </row>
+    <row r="2201">
+      <c r="A2201" s="2" t="n">
+        <v>45841.25</v>
+      </c>
+      <c r="B2201" t="n">
+        <v>591.39</v>
+      </c>
+    </row>
+    <row r="2202">
+      <c r="A2202" s="2" t="n">
+        <v>45841.33333333334</v>
+      </c>
+      <c r="B2202" t="n">
+        <v>591.367</v>
+      </c>
+    </row>
+    <row r="2203">
+      <c r="A2203" s="2" t="n">
+        <v>45841.41666666666</v>
+      </c>
+      <c r="B2203" t="n">
+        <v>591.361</v>
+      </c>
+    </row>
+    <row r="2204">
+      <c r="A2204" s="2" t="n">
+        <v>45841.5</v>
+      </c>
+      <c r="B2204" t="n">
+        <v>591.338</v>
+      </c>
+    </row>
+    <row r="2205">
+      <c r="A2205" s="2" t="n">
+        <v>45841.58333333334</v>
+      </c>
+      <c r="B2205" t="n">
+        <v>591.322</v>
+      </c>
+    </row>
+    <row r="2206">
+      <c r="A2206" s="2" t="n">
+        <v>45841.66666666666</v>
+      </c>
+      <c r="B2206" t="n">
+        <v>591.2910000000001</v>
+      </c>
+    </row>
+    <row r="2207">
+      <c r="A2207" s="2" t="n">
+        <v>45841.75</v>
+      </c>
+      <c r="B2207" t="n">
+        <v>591.279</v>
+      </c>
+    </row>
+    <row r="2208">
+      <c r="A2208" s="2" t="n">
+        <v>45841.83333333334</v>
+      </c>
+      <c r="B2208" t="n">
+        <v>591.284</v>
+      </c>
+    </row>
+    <row r="2209">
+      <c r="A2209" s="2" t="n">
+        <v>45841.91666666666</v>
+      </c>
+      <c r="B2209" t="n">
+        <v>591.285</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
